--- a/artfynd/A 48400-2023 artfynd.xlsx
+++ b/artfynd/A 48400-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,420 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126305050</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nappo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>490729</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6837815</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126305042</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98262</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nappo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>490710</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6837836</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126305013</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98366</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nappo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>490657</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6837890</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126304929</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nappo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>490569</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6837883</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48400-2023 artfynd.xlsx
+++ b/artfynd/A 48400-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126261984</v>
       </c>
       <c r="B2" t="n">
-        <v>98249</v>
+        <v>98253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126305050</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>126305042</v>
       </c>
       <c r="B4" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126305013</v>
       </c>
       <c r="B5" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>126304929</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 48400-2023 artfynd.xlsx
+++ b/artfynd/A 48400-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126261984</v>
       </c>
       <c r="B2" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>126305042</v>
       </c>
       <c r="B4" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126305013</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48400-2023 artfynd.xlsx
+++ b/artfynd/A 48400-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126261984</v>
       </c>
       <c r="B2" t="n">
-        <v>98256</v>
+        <v>98265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126305050</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>126305042</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126305013</v>
       </c>
       <c r="B5" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>126304929</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
